--- a/docs/細谷_質問票0701_PTU研修.xlsx
+++ b/docs/細谷_質問票0701_PTU研修.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\122615\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\mei3336\traning\ptu-training-hosoya\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B00EE545-98F7-4D75-B646-5A6048E9495A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D0D9C48-E6E3-4D08-B9E5-19A09C66E478}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{DB94A49D-4A1A-44CB-9F65-577CCB2B79DF}"/>
+    <workbookView xWindow="1860" yWindow="1860" windowWidth="14400" windowHeight="8170" xr2:uid="{DB94A49D-4A1A-44CB-9F65-577CCB2B79DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -535,7 +535,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -569,6 +569,9 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -584,10 +587,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1512,7 +1511,7 @@
       <c r="G31" s="2"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="1"/>
+      <c r="A32" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -1521,6 +1520,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x0101003355BCCBC65C804784C31EE3EEBC17F0" ma:contentTypeVersion="10" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="d94cf416ea8ef8881753f99440820e8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="37c510ec-9db8-4ebd-830f-5f9c54ea817e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="f9c6532e71801728e242bc209bb4bc82" ns3:_="">
     <xsd:import namespace="37c510ec-9db8-4ebd-830f-5f9c54ea817e"/>
@@ -1702,15 +1710,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1720,6 +1719,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9121D3F6-3CA4-43B9-98BC-C9CD29A77FC7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5F8EAC5E-B6C3-4B79-A358-31462275F272}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1733,14 +1740,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9121D3F6-3CA4-43B9-98BC-C9CD29A77FC7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
